--- a/modelos/xlsx/14_lista_de_marcos.xlsx
+++ b/modelos/xlsx/14_lista_de_marcos.xlsx
@@ -278,7 +278,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1552575" cy="247650"/>
+    <ext cx="2047875" cy="247650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -308,7 +308,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1552575" cy="247650"/>
+    <ext cx="2047875" cy="247650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
